--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/25.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/25.xlsx
@@ -426,13 +426,13 @@
         <v>-6.376351581153114</v>
       </c>
       <c r="E2">
-        <v>-29.08129609471568</v>
+        <v>-27.28555689781804</v>
       </c>
       <c r="F2">
-        <v>-5.520619083406492</v>
+        <v>-4.893121663744436</v>
       </c>
       <c r="G2">
-        <v>-18.84667928655547</v>
+        <v>-15.24547792246605</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.506618240487916</v>
       </c>
       <c r="E3">
-        <v>-29.63223250672586</v>
+        <v>-27.73945943302887</v>
       </c>
       <c r="F3">
-        <v>-5.561578538005317</v>
+        <v>-4.428863152845453</v>
       </c>
       <c r="G3">
-        <v>-18.67976846765886</v>
+        <v>-14.77972492821067</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.65284076871457</v>
       </c>
       <c r="E4">
-        <v>-29.86867545585135</v>
+        <v>-26.2071325122094</v>
       </c>
       <c r="F4">
-        <v>-5.44964125086502</v>
+        <v>-4.241556857561443</v>
       </c>
       <c r="G4">
-        <v>-18.63357050871266</v>
+        <v>-15.94272437896181</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.778271103487955</v>
       </c>
       <c r="E5">
-        <v>-30.0230330208768</v>
+        <v>-27.97266225900187</v>
       </c>
       <c r="F5">
-        <v>-5.38120899135235</v>
+        <v>-4.502345140045589</v>
       </c>
       <c r="G5">
-        <v>-18.65401087841722</v>
+        <v>-15.94045377364268</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.870799794822148</v>
       </c>
       <c r="E6">
-        <v>-30.59623367534569</v>
+        <v>-28.21794705362733</v>
       </c>
       <c r="F6">
-        <v>-5.484407830760515</v>
+        <v>-4.20454208853475</v>
       </c>
       <c r="G6">
-        <v>-18.59400553914887</v>
+        <v>-14.85608715695285</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.908790889474172</v>
       </c>
       <c r="E7">
-        <v>-31.19262690944486</v>
+        <v>-28.07294531590173</v>
       </c>
       <c r="F7">
-        <v>-5.451110774637586</v>
+        <v>-4.548707206845472</v>
       </c>
       <c r="G7">
-        <v>-18.64012802999921</v>
+        <v>-14.77291475286404</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.865570210905977</v>
       </c>
       <c r="E8">
-        <v>-31.58268928233256</v>
+        <v>-29.15152366962663</v>
       </c>
       <c r="F8">
-        <v>-5.115345301791251</v>
+        <v>-3.730048270006777</v>
       </c>
       <c r="G8">
-        <v>-18.42622683714979</v>
+        <v>-16.74388548163441</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.722845277225172</v>
       </c>
       <c r="E9">
-        <v>-32.04394605933183</v>
+        <v>-29.43517369604508</v>
       </c>
       <c r="F9">
-        <v>-5.032183013122</v>
+        <v>-3.965531585070203</v>
       </c>
       <c r="G9">
-        <v>-18.24793510127424</v>
+        <v>-16.70082272988826</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.457166953662173</v>
       </c>
       <c r="E10">
-        <v>-33.06770723519389</v>
+        <v>-29.60529940756524</v>
       </c>
       <c r="F10">
-        <v>-5.181427482982179</v>
+        <v>-3.550816071797853</v>
       </c>
       <c r="G10">
-        <v>-18.20522015901339</v>
+        <v>-17.65648014968731</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.057394270112343</v>
       </c>
       <c r="E11">
-        <v>-33.3689277407621</v>
+        <v>-30.61634915688776</v>
       </c>
       <c r="F11">
-        <v>-5.149406941026964</v>
+        <v>-3.013384554739979</v>
       </c>
       <c r="G11">
-        <v>-17.68290710812708</v>
+        <v>-16.84283728020259</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.522535975546061</v>
       </c>
       <c r="E12">
-        <v>-33.49059878040018</v>
+        <v>-31.16194423380589</v>
       </c>
       <c r="F12">
-        <v>-5.064122375071741</v>
+        <v>-3.136832006942175</v>
       </c>
       <c r="G12">
-        <v>-17.64571118052922</v>
+        <v>-15.49693925850643</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.859632905441451</v>
       </c>
       <c r="E13">
-        <v>-33.76033054195606</v>
+        <v>-32.06550838831936</v>
       </c>
       <c r="F13">
-        <v>-5.117190904364689</v>
+        <v>-3.117697548304909</v>
       </c>
       <c r="G13">
-        <v>-16.99447073151843</v>
+        <v>-15.56675873145908</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.098603406454179</v>
       </c>
       <c r="E14">
-        <v>-34.84219430357352</v>
+        <v>-32.52991924746498</v>
       </c>
       <c r="F14">
-        <v>-4.937257907332997</v>
+        <v>-2.375087709247625</v>
       </c>
       <c r="G14">
-        <v>-16.91250417635272</v>
+        <v>-12.70059365256554</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.271895130721455</v>
       </c>
       <c r="E15">
-        <v>-35.42531231611921</v>
+        <v>-34.33762720116489</v>
       </c>
       <c r="F15">
-        <v>-4.770423884041773</v>
+        <v>-2.740629676754991</v>
       </c>
       <c r="G15">
-        <v>-16.15715056726075</v>
+        <v>-14.18287072654767</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.426185210827748</v>
       </c>
       <c r="E16">
-        <v>-35.76019523322344</v>
+        <v>-32.8466724188795</v>
       </c>
       <c r="F16">
-        <v>-4.668590194113422</v>
+        <v>-2.74954788021353</v>
       </c>
       <c r="G16">
-        <v>-15.95431201289899</v>
+        <v>-14.48165055869681</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.608709856690163</v>
       </c>
       <c r="E17">
-        <v>-36.65285029385242</v>
+        <v>-35.29336843319472</v>
       </c>
       <c r="F17">
-        <v>-4.635973227628192</v>
+        <v>-2.695648498415575</v>
       </c>
       <c r="G17">
-        <v>-15.82483172894174</v>
+        <v>-13.73129753126143</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.8575775597725618</v>
       </c>
       <c r="E18">
-        <v>-37.28408787120362</v>
+        <v>-37.38107193478889</v>
       </c>
       <c r="F18">
-        <v>-4.602010992480815</v>
+        <v>-2.387508250085201</v>
       </c>
       <c r="G18">
-        <v>-15.35078872841643</v>
+        <v>-12.76905962162492</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.2094448478805758</v>
       </c>
       <c r="E19">
-        <v>-38.29805848626109</v>
+        <v>-36.5194097502684</v>
       </c>
       <c r="F19">
-        <v>-4.548214328240806</v>
+        <v>-2.516525644703821</v>
       </c>
       <c r="G19">
-        <v>-14.69597010729506</v>
+        <v>-12.02609262391985</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.3231233080307297</v>
       </c>
       <c r="E20">
-        <v>-38.43809928071129</v>
+        <v>-35.03979879537223</v>
       </c>
       <c r="F20">
-        <v>-4.30543723819573</v>
+        <v>-1.805957056786822</v>
       </c>
       <c r="G20">
-        <v>-14.74615967226833</v>
+        <v>-12.02953790655727</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.7361893703563337</v>
       </c>
       <c r="E21">
-        <v>-39.24276382713423</v>
+        <v>-36.60657155373104</v>
       </c>
       <c r="F21">
-        <v>-3.99910034570125</v>
+        <v>-1.685696333983195</v>
       </c>
       <c r="G21">
-        <v>-14.5732146869239</v>
+        <v>-12.51863022976498</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.036213800768555</v>
       </c>
       <c r="E22">
-        <v>-39.69093105001434</v>
+        <v>-38.27110048049342</v>
       </c>
       <c r="F22">
-        <v>-4.006660026619199</v>
+        <v>-2.507879974120803</v>
       </c>
       <c r="G22">
-        <v>-14.19230423853108</v>
+        <v>-11.07000372348573</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.239926663964822</v>
       </c>
       <c r="E23">
-        <v>-39.73655089716762</v>
+        <v>-37.70722621824333</v>
       </c>
       <c r="F23">
-        <v>-3.997678038870644</v>
+        <v>-1.208391864857523</v>
       </c>
       <c r="G23">
-        <v>-14.281292607834</v>
+        <v>-11.33104458586891</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.358145494970073</v>
       </c>
       <c r="E24">
-        <v>-40.51095844450831</v>
+        <v>-38.84267088431955</v>
       </c>
       <c r="F24">
-        <v>-3.818908898039885</v>
+        <v>-1.625746556675192</v>
       </c>
       <c r="G24">
-        <v>-13.80493142427693</v>
+        <v>-10.99901449504714</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.40626881716469</v>
       </c>
       <c r="E25">
-        <v>-40.52122902355771</v>
+        <v>-40.99143859367015</v>
       </c>
       <c r="F25">
-        <v>-3.776423590685104</v>
+        <v>-1.609140275351271</v>
       </c>
       <c r="G25">
-        <v>-13.97138779398756</v>
+        <v>-11.30399747655441</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.394298568131621</v>
       </c>
       <c r="E26">
-        <v>-40.55970067448987</v>
+        <v>-39.49927244458771</v>
       </c>
       <c r="F26">
-        <v>-3.722475335210383</v>
+        <v>-1.360105697945447</v>
       </c>
       <c r="G26">
-        <v>-14.02179391958375</v>
+        <v>-11.84677386569619</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.328518480319442</v>
       </c>
       <c r="E27">
-        <v>-40.78916750940655</v>
+        <v>-38.11703726627847</v>
       </c>
       <c r="F27">
-        <v>-3.67136092462064</v>
+        <v>-1.8034355064127</v>
       </c>
       <c r="G27">
-        <v>-14.31924977883365</v>
+        <v>-10.95528893654598</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.215928016956466</v>
       </c>
       <c r="E28">
-        <v>-40.79859579229051</v>
+        <v>-40.85033360782815</v>
       </c>
       <c r="F28">
-        <v>-3.548426231840776</v>
+        <v>-1.316019984768457</v>
       </c>
       <c r="G28">
-        <v>-14.48586364717914</v>
+        <v>-10.90986370527703</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.060874155930624</v>
       </c>
       <c r="E29">
-        <v>-40.87638365455727</v>
+        <v>-40.33893530237894</v>
       </c>
       <c r="F29">
-        <v>-3.797885761724236</v>
+        <v>-1.479813071324003</v>
       </c>
       <c r="G29">
-        <v>-14.30623809473968</v>
+        <v>-9.687700548587538</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.8690951741040713</v>
       </c>
       <c r="E30">
-        <v>-41.1072429952313</v>
+        <v>-39.99381350554337</v>
       </c>
       <c r="F30">
-        <v>-3.779420623948432</v>
+        <v>-1.603112245761099</v>
       </c>
       <c r="G30">
-        <v>-14.17301721820466</v>
+        <v>-10.45973260686617</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.6489396709783209</v>
       </c>
       <c r="E31">
-        <v>-40.44994857843997</v>
+        <v>-39.5739537736852</v>
       </c>
       <c r="F31">
-        <v>-3.735556913235393</v>
+        <v>-2.056198565498525</v>
       </c>
       <c r="G31">
-        <v>-14.4376296902553</v>
+        <v>-12.43482126869364</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.4105697130777782</v>
       </c>
       <c r="E32">
-        <v>-39.90534523732952</v>
+        <v>-40.5668013217339</v>
       </c>
       <c r="F32">
-        <v>-3.594403107798357</v>
+        <v>-2.213923860828564</v>
       </c>
       <c r="G32">
-        <v>-14.06712071420592</v>
+        <v>-9.957482585205081</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.1659620033541372</v>
       </c>
       <c r="E33">
-        <v>-39.88107488088541</v>
+        <v>-41.24331458221378</v>
       </c>
       <c r="F33">
-        <v>-3.490433886705588</v>
+        <v>-1.963021314929428</v>
       </c>
       <c r="G33">
-        <v>-14.55359790383076</v>
+        <v>-10.61691296322824</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.07017842845618037</v>
       </c>
       <c r="E34">
-        <v>-39.91411236300837</v>
+        <v>-38.30770187166042</v>
       </c>
       <c r="F34">
-        <v>-3.617941995916308</v>
+        <v>-2.348083760283764</v>
       </c>
       <c r="G34">
-        <v>-14.25813046484588</v>
+        <v>-10.22213935374677</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.2840434707221541</v>
       </c>
       <c r="E35">
-        <v>-39.46133062511444</v>
+        <v>-38.31426363049754</v>
       </c>
       <c r="F35">
-        <v>-3.507634107457318</v>
+        <v>-1.446830794814138</v>
       </c>
       <c r="G35">
-        <v>-14.68180179260138</v>
+        <v>-11.49465941770906</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.462121911681895</v>
       </c>
       <c r="E36">
-        <v>-39.14740095724371</v>
+        <v>-37.6476971631755</v>
       </c>
       <c r="F36">
-        <v>-3.417056273798206</v>
+        <v>-2.016640708545237</v>
       </c>
       <c r="G36">
-        <v>-15.11026042261211</v>
+        <v>-12.67055735041039</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.5911470017245146</v>
       </c>
       <c r="E37">
-        <v>-38.47408253517624</v>
+        <v>-38.29063631736252</v>
       </c>
       <c r="F37">
-        <v>-3.388108146539974</v>
+        <v>-2.054903827247949</v>
       </c>
       <c r="G37">
-        <v>-14.95119664507491</v>
+        <v>-10.92760855147051</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.6623667150824418</v>
       </c>
       <c r="E38">
-        <v>-38.59593924224864</v>
+        <v>-37.27004507330583</v>
       </c>
       <c r="F38">
-        <v>-3.302488091786617</v>
+        <v>-1.830205027401569</v>
       </c>
       <c r="G38">
-        <v>-14.61210208423566</v>
+        <v>-10.88560563428805</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.6692920762132892</v>
       </c>
       <c r="E39">
-        <v>-37.70878627753898</v>
+        <v>-36.49610395878793</v>
       </c>
       <c r="F39">
-        <v>-3.529049889921893</v>
+        <v>-1.430984954765987</v>
       </c>
       <c r="G39">
-        <v>-14.61201677247511</v>
+        <v>-12.05838312528634</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.6107648944302668</v>
       </c>
       <c r="E40">
-        <v>-37.43343920821359</v>
+        <v>-35.97366749794502</v>
       </c>
       <c r="F40">
-        <v>-3.456611645649285</v>
+        <v>-1.939809631935583</v>
       </c>
       <c r="G40">
-        <v>-15.37513375177673</v>
+        <v>-11.1380332900777</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.4921654075039784</v>
       </c>
       <c r="E41">
-        <v>-36.97280962486438</v>
+        <v>-36.80695200009644</v>
       </c>
       <c r="F41">
-        <v>-3.336028687925969</v>
+        <v>-1.809978780527413</v>
       </c>
       <c r="G41">
-        <v>-15.10404578897852</v>
+        <v>-11.40296240000882</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.3221788060134998</v>
       </c>
       <c r="E42">
-        <v>-36.5006324327956</v>
+        <v>-34.40520109030734</v>
       </c>
       <c r="F42">
-        <v>-3.272193039131434</v>
+        <v>-1.499633418170787</v>
       </c>
       <c r="G42">
-        <v>-15.65294657816101</v>
+        <v>-11.41344262166969</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.1158445258969797</v>
       </c>
       <c r="E43">
-        <v>-36.04682046706493</v>
+        <v>-35.40718936314052</v>
       </c>
       <c r="F43">
-        <v>-3.474594673596659</v>
+        <v>-1.741435519782768</v>
       </c>
       <c r="G43">
-        <v>-15.08309847054303</v>
+        <v>-11.81796145918271</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.1092088036064529</v>
       </c>
       <c r="E44">
-        <v>-35.26814936144601</v>
+        <v>-32.81128692298356</v>
       </c>
       <c r="F44">
-        <v>-3.193665466080846</v>
+        <v>-1.492992396702544</v>
       </c>
       <c r="G44">
-        <v>-15.21683121764132</v>
+        <v>-12.13344763090176</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.3342258811811865</v>
       </c>
       <c r="E45">
-        <v>-35.39801014632697</v>
+        <v>-33.21469244453485</v>
       </c>
       <c r="F45">
-        <v>-3.427356194084615</v>
+        <v>-1.862870039196162</v>
       </c>
       <c r="G45">
-        <v>-15.68282045984898</v>
+        <v>-12.02902931721555</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.540370391453175</v>
       </c>
       <c r="E46">
-        <v>-34.2111152228126</v>
+        <v>-30.67984289094931</v>
       </c>
       <c r="F46">
-        <v>-3.124306263444443</v>
+        <v>-1.768256399550611</v>
       </c>
       <c r="G46">
-        <v>-15.36843841918468</v>
+        <v>-11.90962566466736</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.7104577997686236</v>
       </c>
       <c r="E47">
-        <v>-33.86382428692735</v>
+        <v>-33.27932056133532</v>
       </c>
       <c r="F47">
-        <v>-3.126490668285626</v>
+        <v>-1.60830279590704</v>
       </c>
       <c r="G47">
-        <v>-15.86103016518554</v>
+        <v>-12.22060015674217</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.8307521417572215</v>
       </c>
       <c r="E48">
-        <v>-33.7415215251652</v>
+        <v>-31.52767058737636</v>
       </c>
       <c r="F48">
-        <v>-3.275642360996691</v>
+        <v>-0.8603218226100043</v>
       </c>
       <c r="G48">
-        <v>-15.9511800869205</v>
+        <v>-11.5206598173461</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.8914102573239715</v>
       </c>
       <c r="E49">
-        <v>-32.94611770808794</v>
+        <v>-29.75278727752105</v>
       </c>
       <c r="F49">
-        <v>-3.29663319098363</v>
+        <v>-0.8083749027804473</v>
       </c>
       <c r="G49">
-        <v>-15.6832716278134</v>
+        <v>-12.35137980443696</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.887074594455881</v>
       </c>
       <c r="E50">
-        <v>-32.02351358460923</v>
+        <v>-28.25436504159702</v>
       </c>
       <c r="F50">
-        <v>-3.048154448105085</v>
+        <v>-1.482873060509945</v>
       </c>
       <c r="G50">
-        <v>-15.47533241453749</v>
+        <v>-12.67609277118117</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.8189034665498774</v>
       </c>
       <c r="E51">
-        <v>-32.23754964434476</v>
+        <v>-30.53064325781859</v>
       </c>
       <c r="F51">
-        <v>-3.26706710164291</v>
+        <v>-1.700824807860523</v>
       </c>
       <c r="G51">
-        <v>-16.11328063501097</v>
+        <v>-12.2818769693648</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.6912651276285994</v>
       </c>
       <c r="E52">
-        <v>-31.71490940217151</v>
+        <v>-26.79034109423525</v>
       </c>
       <c r="F52">
-        <v>-3.160345215670639</v>
+        <v>-0.8286732176186464</v>
       </c>
       <c r="G52">
-        <v>-16.42958054967676</v>
+        <v>-12.4090472733442</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.5140851813726758</v>
       </c>
       <c r="E53">
-        <v>-31.38826830776124</v>
+        <v>-29.47947575726212</v>
       </c>
       <c r="F53">
-        <v>-3.135171958666965</v>
+        <v>-1.539735512507714</v>
       </c>
       <c r="G53">
-        <v>-16.11739200562495</v>
+        <v>-13.75338671479962</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.300435230738158</v>
       </c>
       <c r="E54">
-        <v>-30.61042138441172</v>
+        <v>-27.7209968444996</v>
       </c>
       <c r="F54">
-        <v>-3.182547118800471</v>
+        <v>-1.112171192450541</v>
       </c>
       <c r="G54">
-        <v>-16.3410646762784</v>
+        <v>-12.03975891171494</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.06450080003791037</v>
       </c>
       <c r="E55">
-        <v>-30.60877754834694</v>
+        <v>-27.07862374956354</v>
       </c>
       <c r="F55">
-        <v>-3.292781282560612</v>
+        <v>-1.2634219681603</v>
       </c>
       <c r="G55">
-        <v>-16.46387587741608</v>
+        <v>-13.24655282661999</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.177569399889043</v>
       </c>
       <c r="E56">
-        <v>-29.81064306144305</v>
+        <v>-26.68937876623423</v>
       </c>
       <c r="F56">
-        <v>-3.222298813726014</v>
+        <v>-1.091732055153866</v>
       </c>
       <c r="G56">
-        <v>-16.38620116005012</v>
+        <v>-12.76601464801775</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.4115615373334526</v>
       </c>
       <c r="E57">
-        <v>-29.77502661337272</v>
+        <v>-26.67188074266859</v>
       </c>
       <c r="F57">
-        <v>-3.27561833834201</v>
+        <v>-1.047889053625896</v>
       </c>
       <c r="G57">
-        <v>-16.59644543147154</v>
+        <v>-12.89722085451527</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.6258638853231739</v>
       </c>
       <c r="E58">
-        <v>-28.79687622771593</v>
+        <v>-24.28463679936307</v>
       </c>
       <c r="F58">
-        <v>-3.248711308364276</v>
+        <v>-0.9662749836324779</v>
       </c>
       <c r="G58">
-        <v>-16.71110771886634</v>
+        <v>-13.86753056918802</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.8107938944344927</v>
       </c>
       <c r="E59">
-        <v>-29.01885296662391</v>
+        <v>-25.29603071271017</v>
       </c>
       <c r="F59">
-        <v>-3.469116679961946</v>
+        <v>-0.9477949352434237</v>
       </c>
       <c r="G59">
-        <v>-16.73127574718147</v>
+        <v>-13.00832957896118</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.9619169249993852</v>
       </c>
       <c r="E60">
-        <v>-28.43752370131125</v>
+        <v>-22.41706694775577</v>
       </c>
       <c r="F60">
-        <v>-3.287705047116257</v>
+        <v>-1.039302197128477</v>
       </c>
       <c r="G60">
-        <v>-16.66187791119921</v>
+        <v>-13.25969411896557</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.077748002155148</v>
       </c>
       <c r="E61">
-        <v>-28.23193098136302</v>
+        <v>-25.89973969656874</v>
       </c>
       <c r="F61">
-        <v>-3.489333814794671</v>
+        <v>-1.815692030504522</v>
       </c>
       <c r="G61">
-        <v>-16.94313602022091</v>
+        <v>-13.69415738443008</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.161108960512961</v>
       </c>
       <c r="E62">
-        <v>-27.90105349951858</v>
+        <v>-24.46650031551111</v>
       </c>
       <c r="F62">
-        <v>-3.622416836626231</v>
+        <v>-1.055321994331216</v>
       </c>
       <c r="G62">
-        <v>-17.14431591708437</v>
+        <v>-13.76493989591042</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.218606302477758</v>
       </c>
       <c r="E63">
-        <v>-28.09897045602381</v>
+        <v>-23.61698123404219</v>
       </c>
       <c r="F63">
-        <v>-3.625987100132297</v>
+        <v>-1.791418380500288</v>
       </c>
       <c r="G63">
-        <v>-16.98498636060085</v>
+        <v>-14.08642250002936</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.256719136009846</v>
       </c>
       <c r="E64">
-        <v>-27.39515955422569</v>
+        <v>-24.04674700279213</v>
       </c>
       <c r="F64">
-        <v>-3.553022842558911</v>
+        <v>-1.40668976720928</v>
       </c>
       <c r="G64">
-        <v>-17.79888188414565</v>
+        <v>-14.62947451178213</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.283721385054365</v>
       </c>
       <c r="E65">
-        <v>-27.08635385469463</v>
+        <v>-21.85482972885945</v>
       </c>
       <c r="F65">
-        <v>-3.711641946316572</v>
+        <v>-1.95658324347487</v>
       </c>
       <c r="G65">
-        <v>-17.11228463222107</v>
+        <v>-13.65274180590677</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.305207858785359</v>
       </c>
       <c r="E66">
-        <v>-27.3429779482353</v>
+        <v>-21.79514896991236</v>
       </c>
       <c r="F66">
-        <v>-3.96767291480644</v>
+        <v>-1.684355207158063</v>
       </c>
       <c r="G66">
-        <v>-17.40482358096414</v>
+        <v>-14.58775870148614</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.32517857340199</v>
       </c>
       <c r="E67">
-        <v>-27.13873471354136</v>
+        <v>-21.78790341150009</v>
       </c>
       <c r="F67">
-        <v>-4.050962772055722</v>
+        <v>-2.788302220786103</v>
       </c>
       <c r="G67">
-        <v>-17.26314043402732</v>
+        <v>-13.88089334398886</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.344574364666635</v>
       </c>
       <c r="E68">
-        <v>-26.5566990062835</v>
+        <v>-22.95776674427161</v>
       </c>
       <c r="F68">
-        <v>-3.96116608885745</v>
+        <v>-2.194950105467442</v>
       </c>
       <c r="G68">
-        <v>-17.5334294193758</v>
+        <v>-14.11939057364788</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.36095979845889</v>
       </c>
       <c r="E69">
-        <v>-25.91504141024066</v>
+        <v>-21.31021733080098</v>
       </c>
       <c r="F69">
-        <v>-4.06473023829025</v>
+        <v>-2.70561872847567</v>
       </c>
       <c r="G69">
-        <v>-17.46572797493977</v>
+        <v>-13.54755568637565</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.370476177734762</v>
       </c>
       <c r="E70">
-        <v>-26.46201767173113</v>
+        <v>-23.08291565194758</v>
       </c>
       <c r="F70">
-        <v>-4.117863380240616</v>
+        <v>-2.764058392008369</v>
       </c>
       <c r="G70">
-        <v>-17.37314174619692</v>
+        <v>-11.95103796196911</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.366482508477081</v>
       </c>
       <c r="E71">
-        <v>-26.14453541600137</v>
+        <v>-20.69692156746817</v>
       </c>
       <c r="F71">
-        <v>-4.247332235093761</v>
+        <v>-2.773221792218137</v>
       </c>
       <c r="G71">
-        <v>-17.5804526055442</v>
+        <v>-13.89747171591795</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.343949889676565</v>
       </c>
       <c r="E72">
-        <v>-26.1694057952515</v>
+        <v>-21.33276460288517</v>
       </c>
       <c r="F72">
-        <v>-4.19636361716691</v>
+        <v>-2.87362654837666</v>
       </c>
       <c r="G72">
-        <v>-17.14504434827056</v>
+        <v>-14.00892824984917</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.296807169641473</v>
       </c>
       <c r="E73">
-        <v>-26.09839026586321</v>
+        <v>-20.68933184503132</v>
       </c>
       <c r="F73">
-        <v>-4.421417786629092</v>
+        <v>-2.812450787312514</v>
       </c>
       <c r="G73">
-        <v>-16.72623907208772</v>
+        <v>-13.17229222028664</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.220917176271713</v>
       </c>
       <c r="E74">
-        <v>-26.61934591570561</v>
+        <v>-21.85615204326968</v>
       </c>
       <c r="F74">
-        <v>-4.44334052994418</v>
+        <v>-2.852429454906424</v>
       </c>
       <c r="G74">
-        <v>-17.0828077783418</v>
+        <v>-12.30152820528432</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.113723921452181</v>
       </c>
       <c r="E75">
-        <v>-26.88918862487467</v>
+        <v>-21.74449798813657</v>
       </c>
       <c r="F75">
-        <v>-4.439238454565517</v>
+        <v>-3.303003336311158</v>
       </c>
       <c r="G75">
-        <v>-16.90579735948521</v>
+        <v>-13.61960474937794</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.9743647118220586</v>
       </c>
       <c r="E76">
-        <v>-27.16139519747574</v>
+        <v>-20.73939865366012</v>
       </c>
       <c r="F76">
-        <v>-4.48046961367246</v>
+        <v>-4.394075863764888</v>
       </c>
       <c r="G76">
-        <v>-16.60682557587485</v>
+        <v>-12.49714479099373</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.8070238271459867</v>
       </c>
       <c r="E77">
-        <v>-26.93104983860158</v>
+        <v>-22.97046911386312</v>
       </c>
       <c r="F77">
-        <v>-4.590846256625882</v>
+        <v>-3.494210413694951</v>
       </c>
       <c r="G77">
-        <v>-16.21031291896687</v>
+        <v>-12.12428646030779</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.6175099563387663</v>
       </c>
       <c r="E78">
-        <v>-27.2476852696919</v>
+        <v>-22.61031504755909</v>
       </c>
       <c r="F78">
-        <v>-4.596171830658481</v>
+        <v>-3.17954925716974</v>
       </c>
       <c r="G78">
-        <v>-15.88572791986348</v>
+        <v>-11.8112874545308</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.415830080352957</v>
       </c>
       <c r="E79">
-        <v>-27.50711701711732</v>
+        <v>-23.8946446178225</v>
       </c>
       <c r="F79">
-        <v>-4.686999002905835</v>
+        <v>-3.685288265763908</v>
       </c>
       <c r="G79">
-        <v>-16.01517539160513</v>
+        <v>-12.03329490524283</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.214639812565533</v>
       </c>
       <c r="E80">
-        <v>-28.36762670500286</v>
+        <v>-23.74378303473097</v>
       </c>
       <c r="F80">
-        <v>-4.615252445414565</v>
+        <v>-3.967614100720841</v>
       </c>
       <c r="G80">
-        <v>-15.65440179992263</v>
+        <v>-10.96608743669811</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.02610483877380808</v>
       </c>
       <c r="E81">
-        <v>-28.23899087234098</v>
+        <v>-24.10839764793255</v>
       </c>
       <c r="F81">
-        <v>-4.864745938361539</v>
+        <v>-3.384130326271731</v>
       </c>
       <c r="G81">
-        <v>-15.74035339867228</v>
+        <v>-10.94915961467294</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.1363756551993166</v>
       </c>
       <c r="E82">
-        <v>-28.43838411137271</v>
+        <v>-23.47785745557854</v>
       </c>
       <c r="F82">
-        <v>-4.74437504269334</v>
+        <v>-4.071126891374667</v>
       </c>
       <c r="G82">
-        <v>-15.16483041836724</v>
+        <v>-10.41432706292657</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.2627744559225524</v>
       </c>
       <c r="E83">
-        <v>-29.65886219812796</v>
+        <v>-22.89759238165768</v>
       </c>
       <c r="F83">
-        <v>-4.902181518028854</v>
+        <v>-3.547848031393622</v>
       </c>
       <c r="G83">
-        <v>-14.69810618253026</v>
+        <v>-10.06047028629137</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.3463507470358463</v>
       </c>
       <c r="E84">
-        <v>-29.91146953522383</v>
+        <v>-24.43776261945843</v>
       </c>
       <c r="F84">
-        <v>-4.90404451631775</v>
+        <v>-3.386073676198698</v>
       </c>
       <c r="G84">
-        <v>-14.91739842240185</v>
+        <v>-10.81984339179366</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.3827862594446393</v>
       </c>
       <c r="E85">
-        <v>-30.6663208675624</v>
+        <v>-24.32119064155298</v>
       </c>
       <c r="F85">
-        <v>-5.061081438336064</v>
+        <v>-4.444264987965704</v>
       </c>
       <c r="G85">
-        <v>-14.3712046410059</v>
+        <v>-10.43781076562752</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.3735261846787201</v>
       </c>
       <c r="E86">
-        <v>-31.35833735880755</v>
+        <v>-27.05879809035796</v>
       </c>
       <c r="F86">
-        <v>-5.105288921521265</v>
+        <v>-4.389920772872446</v>
       </c>
       <c r="G86">
-        <v>-14.26032560206915</v>
+        <v>-10.18073033766658</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.3219456766036453</v>
       </c>
       <c r="E87">
-        <v>-32.03659634601738</v>
+        <v>-29.72497339016594</v>
       </c>
       <c r="F87">
-        <v>-5.059476062309439</v>
+        <v>-4.509203193773367</v>
       </c>
       <c r="G87">
-        <v>-14.07796515145989</v>
+        <v>-8.920964381905852</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.2339452361399791</v>
       </c>
       <c r="E88">
-        <v>-33.29431886724872</v>
+        <v>-29.07251991208881</v>
       </c>
       <c r="F88">
-        <v>-5.151443068103045</v>
+        <v>-4.590302019242244</v>
       </c>
       <c r="G88">
-        <v>-14.11230313507948</v>
+        <v>-10.36871152080717</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.1185572731456542</v>
       </c>
       <c r="E89">
-        <v>-34.63467018946102</v>
+        <v>-31.31597348446579</v>
       </c>
       <c r="F89">
-        <v>-5.287812223421511</v>
+        <v>-4.369114668816331</v>
       </c>
       <c r="G89">
-        <v>-14.13706979541017</v>
+        <v>-9.402007868628244</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.01809374269493719</v>
       </c>
       <c r="E90">
-        <v>-35.29684403699562</v>
+        <v>-32.3583059322333</v>
       </c>
       <c r="F90">
-        <v>-5.214998728715434</v>
+        <v>-4.275576250059613</v>
       </c>
       <c r="G90">
-        <v>-13.95253717612855</v>
+        <v>-9.336869058230148</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.1686833386627324</v>
       </c>
       <c r="E91">
-        <v>-36.13639141869965</v>
+        <v>-34.70005003294676</v>
       </c>
       <c r="F91">
-        <v>-5.414171387044548</v>
+        <v>-4.667702184257621</v>
       </c>
       <c r="G91">
-        <v>-13.52013779902493</v>
+        <v>-9.28615777902893</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.3282061961921773</v>
       </c>
       <c r="E92">
-        <v>-37.65245658935756</v>
+        <v>-33.72718664069392</v>
       </c>
       <c r="F92">
-        <v>-5.449604802699296</v>
+        <v>-5.294893936348044</v>
       </c>
       <c r="G92">
-        <v>-13.78775258880246</v>
+        <v>-9.564720364539548</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.4963357196032824</v>
       </c>
       <c r="E93">
-        <v>-39.20547184368107</v>
+        <v>-34.73516382040224</v>
       </c>
       <c r="F93">
-        <v>-5.328408024730506</v>
+        <v>-5.840158495566791</v>
       </c>
       <c r="G93">
-        <v>-14.18628811880184</v>
+        <v>-9.952344192242991</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.6719980215837343</v>
       </c>
       <c r="E94">
-        <v>-40.71232156973338</v>
+        <v>-36.71247897534843</v>
       </c>
       <c r="F94">
-        <v>-5.559852220337882</v>
+        <v>-5.769633779994649</v>
       </c>
       <c r="G94">
-        <v>-14.03120118179468</v>
+        <v>-9.299623912308892</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.8597270642706661</v>
       </c>
       <c r="E95">
-        <v>-41.94329439500141</v>
+        <v>-39.17396498577271</v>
       </c>
       <c r="F95">
-        <v>-5.658428769638427</v>
+        <v>-5.426684705031237</v>
       </c>
       <c r="G95">
-        <v>-14.66316773536529</v>
+        <v>-9.39329294416636</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.065580740286532</v>
       </c>
       <c r="E96">
-        <v>-43.63882751905732</v>
+        <v>-39.70934382532953</v>
       </c>
       <c r="F96">
-        <v>-5.848498498578176</v>
+        <v>-6.614822011275401</v>
       </c>
       <c r="G96">
-        <v>-14.81974434696044</v>
+        <v>-9.486866820598605</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.288965360276709</v>
       </c>
       <c r="E97">
-        <v>-44.85785649413012</v>
+        <v>-43.14706014843136</v>
       </c>
       <c r="F97">
-        <v>-5.85743575448698</v>
+        <v>-5.747296024610757</v>
       </c>
       <c r="G97">
-        <v>-14.99638562839158</v>
+        <v>-9.430347779237168</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.537665808414015</v>
       </c>
       <c r="E98">
-        <v>-46.39643950179118</v>
+        <v>-43.34512880881585</v>
       </c>
       <c r="F98">
-        <v>-5.921550563096259</v>
+        <v>-5.697302395117002</v>
       </c>
       <c r="G98">
-        <v>-15.02768520084713</v>
+        <v>-10.72034691044662</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.797453030932678</v>
       </c>
       <c r="E99">
-        <v>-48.30154134597405</v>
+        <v>-46.05269888952795</v>
       </c>
       <c r="F99">
-        <v>-6.000907331917048</v>
+        <v>-6.015972849871764</v>
       </c>
       <c r="G99">
-        <v>-15.02505366115645</v>
+        <v>-10.72263064065199</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.076253809212806</v>
       </c>
       <c r="E100">
-        <v>-50.03888134206877</v>
+        <v>-47.06457282111987</v>
       </c>
       <c r="F100">
-        <v>-6.048996544751768</v>
+        <v>-5.794541131062025</v>
       </c>
       <c r="G100">
-        <v>-15.77342483076992</v>
+        <v>-11.35327814315571</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.340301256399282</v>
       </c>
       <c r="E101">
-        <v>-51.66752550867587</v>
+        <v>-49.79858013308874</v>
       </c>
       <c r="F101">
-        <v>-5.925558204591002</v>
+        <v>-6.17696108440143</v>
       </c>
       <c r="G101">
-        <v>-15.67652707689796</v>
+        <v>-11.97005264090609</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.610942229595367</v>
       </c>
       <c r="E102">
-        <v>-53.29207480266155</v>
+        <v>-51.11572755448574</v>
       </c>
       <c r="F102">
-        <v>-6.321963484791873</v>
+        <v>-5.614723277099322</v>
       </c>
       <c r="G102">
-        <v>-15.5627605629889</v>
+        <v>-10.89684709935071</v>
       </c>
     </row>
   </sheetData>
